--- a/src/Data/country_data.xlsx
+++ b/src/Data/country_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/mr-risk-assessment/src/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{4BB21942-1E30-4A3E-86F4-D1438ED0EF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A564E2A-06D1-4D86-9D81-7ADF759645F3}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{4BB21942-1E30-4A3E-86F4-D1438ED0EF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74F0AE21-FD85-4C56-B980-FFC59CB5A520}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1098,7 +1098,7 @@
     <t>El equipo subnacional de respuesta rápida fue entrenado en los últimos 2 años</t>
   </si>
   <si>
-    <t>SPA</t>
+    <t>ENG</t>
   </si>
 </sst>
 </file>
@@ -9101,18 +9101,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9339,6 +9339,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6264E33-6917-4678-8EC8-8D88A2F9795C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A51E5E2-41F2-4A1F-A4B0-950DEDB4B143}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -9351,14 +9359,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6264E33-6917-4678-8EC8-8D88A2F9795C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/src/Data/country_data.xlsx
+++ b/src/Data/country_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11116"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/mr-risk-assessment/src/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rafaelleon/mr-risk-assessment/src/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{4BB21942-1E30-4A3E-86F4-D1438ED0EF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74F0AE21-FD85-4C56-B980-FFC59CB5A520}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0A020F-5297-9544-ADF0-FB9F0335CD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="21660" tabRatio="773" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-General" sheetId="1" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
     <t>El equipo subnacional de respuesta rápida fue entrenado en los últimos 2 años</t>
   </si>
   <si>
-    <t>ENG</t>
+    <t>SPA</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1109,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;\-#,###;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2067,7 +2067,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2075,7 +2075,7 @@
       <font>
         <sz val="9"/>
       </font>
-      <numFmt numFmtId="166" formatCode="d/mm/yy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yy"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2096,7 +2096,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2104,7 +2104,7 @@
       <font>
         <sz val="9"/>
       </font>
-      <numFmt numFmtId="166" formatCode="d/mm/yy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yy"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2125,14 +2125,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="9"/>
       </font>
-      <numFmt numFmtId="166" formatCode="d/mm/yy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yy"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2153,14 +2153,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="9"/>
       </font>
-      <numFmt numFmtId="166" formatCode="d/mm/yy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yy"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2181,14 +2181,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="9"/>
       </font>
-      <numFmt numFmtId="166" formatCode="d/mm/yy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yy"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -2262,11 +2262,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2358,7 +2358,7 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -3135,14 +3135,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.453125" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" style="5" customWidth="1"/>
-    <col min="3" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.5" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" customHeight="1">
+    <row r="1" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
         <v>28</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>44</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>87</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>224</v>
       </c>
@@ -3229,18 +3229,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="19.453125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="21.36328125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="24.453125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="20.453125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="27.81640625" style="27" customWidth="1"/>
-    <col min="7" max="16384" width="9.1796875" style="27"/>
+    <col min="1" max="1" width="17.1640625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="27" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="27" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="27" customWidth="1"/>
+    <col min="6" max="6" width="27.83203125" style="27" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36" customHeight="1">
+    <row r="1" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="47" t="s">
         <v>213</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
         <v>89</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>4307.2</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
         <v>89</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>5195.6000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
         <v>89</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>1859.6</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
         <v>89</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>4636.1000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="44" t="s">
         <v>89</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>2553.6999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
         <v>89</v>
       </c>
@@ -3392,25 +3392,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.453125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="8.6328125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" style="27" customWidth="1"/>
-    <col min="7" max="7" width="8.1796875" style="27" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" style="27" customWidth="1"/>
-    <col min="9" max="9" width="7.1796875" style="27" customWidth="1"/>
-    <col min="10" max="11" width="8.1796875" style="27" customWidth="1"/>
-    <col min="12" max="12" width="7.81640625" style="27" customWidth="1"/>
-    <col min="13" max="13" width="7.453125" style="27" customWidth="1"/>
-    <col min="14" max="14" width="7.36328125" style="27" customWidth="1"/>
-    <col min="15" max="15" width="16.6328125" style="27" customWidth="1"/>
-    <col min="16" max="16384" width="9.1796875" style="27"/>
+    <col min="1" max="2" width="9.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="27" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" style="27" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" style="27" customWidth="1"/>
+    <col min="8" max="8" width="7.83203125" style="27" customWidth="1"/>
+    <col min="9" max="9" width="7.1640625" style="27" customWidth="1"/>
+    <col min="10" max="11" width="8.1640625" style="27" customWidth="1"/>
+    <col min="12" max="12" width="7.83203125" style="27" customWidth="1"/>
+    <col min="13" max="13" width="7.5" style="27" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" style="27" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" style="27" customWidth="1"/>
+    <col min="16" max="16384" width="9.1640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="61" customHeight="1">
+    <row r="1" spans="1:15" ht="61" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="58" t="s">
         <v>213</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="59"/>
       <c r="B2" s="59"/>
       <c r="C2" s="62"/>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="O2" s="61"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
         <v>89</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
         <v>89</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
         <v>89</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="44" t="s">
         <v>89</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
         <v>89</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="44" t="s">
         <v>89</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="16.5">
+    <row r="10" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="D10" s="32"/>
     </row>
   </sheetData>
@@ -3792,21 +3792,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.453125" style="27" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" style="27" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="27" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="27" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" style="27" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="27" customWidth="1"/>
     <col min="7" max="7" width="17" style="27" customWidth="1"/>
-    <col min="8" max="8" width="32.1796875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="32.1640625" style="27" customWidth="1"/>
     <col min="9" max="9" width="30" style="27" customWidth="1"/>
-    <col min="10" max="16384" width="9.1796875" style="27"/>
+    <col min="10" max="16384" width="9.1640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="58" customHeight="1">
+    <row r="1" spans="1:9" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="58" t="s">
         <v>213</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="59"/>
       <c r="B2" s="59"/>
       <c r="C2" s="63"/>
@@ -3861,7 +3861,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20.25" customHeight="1">
+    <row r="3" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
         <v>89</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>8.8091353996737354</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
         <v>89</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>-2.8728606356968216</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
         <v>89</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>3.3472803347280333</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="44" t="s">
         <v>89</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>4.7804878048780486</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
         <v>89</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>-1.7364657814096014</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="44" t="s">
         <v>89</v>
       </c>
@@ -4064,24 +4064,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.453125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" style="27" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.453125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" style="27" customWidth="1"/>
-    <col min="7" max="7" width="24.81640625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" style="27" customWidth="1"/>
-    <col min="9" max="9" width="20.1796875" style="27" customWidth="1"/>
+    <col min="1" max="2" width="9.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="27" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" style="27" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="16.1640625" style="27" customWidth="1"/>
+    <col min="9" max="9" width="20.1640625" style="27" customWidth="1"/>
     <col min="10" max="10" width="20" style="27" customWidth="1"/>
-    <col min="11" max="11" width="19.1796875" style="27" customWidth="1"/>
-    <col min="12" max="12" width="21.453125" style="27" customWidth="1"/>
-    <col min="13" max="16" width="20.81640625" style="27" customWidth="1"/>
-    <col min="17" max="16384" width="9.1796875" style="27"/>
+    <col min="11" max="11" width="19.1640625" style="27" customWidth="1"/>
+    <col min="12" max="12" width="21.5" style="27" customWidth="1"/>
+    <col min="13" max="16" width="20.83203125" style="27" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="112.5" customHeight="1">
+    <row r="1" spans="1:12" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="58" t="s">
         <v>213</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="29" customHeight="1">
+    <row r="2" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="59"/>
       <c r="B2" s="59"/>
       <c r="C2" s="63"/>
@@ -4157,7 +4157,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
         <v>89</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
         <v>89</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
         <v>89</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="44" t="s">
         <v>89</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
         <v>89</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="44" t="s">
         <v>89</v>
       </c>
@@ -4405,31 +4405,31 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S112"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.81640625" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" customWidth="1"/>
-    <col min="9" max="9" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="28" width="35.81640625" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="28" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="24" customHeight="1">
+    <row r="1" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4452,7 +4452,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="9"/>
     </row>
-    <row r="2" spans="1:19" ht="15" customHeight="1">
+    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -4475,7 +4475,7 @@
       <c r="R2" s="11"/>
       <c r="S2" s="6"/>
     </row>
-    <row r="3" spans="1:19" ht="16" customHeight="1">
+    <row r="3" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="17" t="str">
@@ -4501,7 +4501,7 @@
       <c r="R3" s="11"/>
       <c r="S3" s="6"/>
     </row>
-    <row r="4" spans="1:19" ht="15" customHeight="1">
+    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -4524,7 +4524,7 @@
       <c r="R4" s="11"/>
       <c r="S4" s="6"/>
     </row>
-    <row r="5" spans="1:19" ht="15" customHeight="1">
+    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -4547,7 +4547,7 @@
       <c r="R5" s="11"/>
       <c r="S5" s="6"/>
     </row>
-    <row r="6" spans="1:19" ht="15" customHeight="1">
+    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -4570,7 +4570,7 @@
       <c r="R6" s="11"/>
       <c r="S6" s="6"/>
     </row>
-    <row r="7" spans="1:19" ht="15" customHeight="1">
+    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4591,7 +4591,7 @@
       <c r="R7" s="11"/>
       <c r="S7" s="6"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -4612,7 +4612,7 @@
       <c r="R8" s="11"/>
       <c r="S8" s="6"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -4633,7 +4633,7 @@
       <c r="R9" s="14"/>
       <c r="S9" s="13"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>66</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>67</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -4772,7 +4772,7 @@
       <c r="R12" s="11"/>
       <c r="S12" s="6"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
         <v>12</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="18">
         <v>2018</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="18">
         <v>2018</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="18">
         <v>2018</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="18">
         <v>2018</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="18">
         <v>2018</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="18">
         <v>2018</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="18">
         <v>2018</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="18">
         <v>2018</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="18">
         <v>2018</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="18">
         <v>2018</v>
       </c>
@@ -5407,7 +5407,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="18">
         <v>2018</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="18">
         <v>2018</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="18">
         <v>2018</v>
       </c>
@@ -5582,7 +5582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="18">
         <v>2018</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="18">
         <v>2018</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="18">
         <v>2018</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="18">
         <v>2018</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="18">
         <v>2018</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="18">
         <v>2018</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="18">
         <v>2018</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="18">
         <v>2018</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="18">
         <v>2018</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="18">
         <v>2018</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="18">
         <v>2018</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="18">
         <v>2018</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="18">
         <v>2018</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="18">
         <v>2018</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="18">
         <v>2018</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="18">
         <v>2018</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="18">
         <v>2018</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="18">
         <v>2018</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="18">
         <v>2018</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="18">
         <v>2018</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="18">
         <v>2018</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="18">
         <v>2018</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="18">
         <v>2018</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="18">
         <v>2018</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="18">
         <v>2018</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="18">
         <v>2018</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="18">
         <v>2018</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="18">
         <v>2018</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="18">
         <v>2018</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="18">
         <v>2018</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="18">
         <v>2018</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="18">
         <v>2018</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="18">
         <v>2018</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="18">
         <v>2018</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="18">
         <v>2018</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="18">
         <v>2018</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="18">
         <v>2018</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="18">
         <v>2018</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="18">
         <v>2018</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="18">
         <v>2018</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="18">
         <v>2018</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="18">
         <v>2018</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="18">
         <v>2018</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="18">
         <v>2018</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="18">
         <v>2018</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="18" t="s">
         <v>2</v>
       </c>
@@ -8226,7 +8226,7 @@
       <c r="R72" s="22"/>
       <c r="S72" s="19"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="25"/>
       <c r="B73" s="25"/>
       <c r="G73" s="26"/>
@@ -8239,7 +8239,7 @@
       <c r="Q73" s="28"/>
       <c r="R73" s="26"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="25"/>
       <c r="B74" s="25"/>
       <c r="G74" s="26"/>
@@ -8252,7 +8252,7 @@
       <c r="Q74" s="28"/>
       <c r="R74" s="26"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="25"/>
       <c r="B75" s="25"/>
       <c r="G75" s="26"/>
@@ -8265,7 +8265,7 @@
       <c r="Q75" s="28"/>
       <c r="R75" s="26"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="25"/>
       <c r="B76" s="25"/>
       <c r="G76" s="26"/>
@@ -8278,7 +8278,7 @@
       <c r="Q76" s="28"/>
       <c r="R76" s="26"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="25"/>
       <c r="B77" s="25"/>
       <c r="G77" s="26"/>
@@ -8291,7 +8291,7 @@
       <c r="Q77" s="28"/>
       <c r="R77" s="26"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="25"/>
       <c r="B78" s="25"/>
       <c r="G78" s="26"/>
@@ -8304,7 +8304,7 @@
       <c r="Q78" s="28"/>
       <c r="R78" s="26"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="25"/>
       <c r="B79" s="25"/>
       <c r="G79" s="26"/>
@@ -8317,7 +8317,7 @@
       <c r="Q79" s="28"/>
       <c r="R79" s="26"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="25"/>
       <c r="B80" s="25"/>
       <c r="G80" s="26"/>
@@ -8330,7 +8330,7 @@
       <c r="Q80" s="28"/>
       <c r="R80" s="26"/>
     </row>
-    <row r="81" spans="1:18">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="25"/>
       <c r="B81" s="25"/>
       <c r="G81" s="26"/>
@@ -8343,7 +8343,7 @@
       <c r="Q81" s="28"/>
       <c r="R81" s="26"/>
     </row>
-    <row r="82" spans="1:18">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A82" s="25"/>
       <c r="B82" s="25"/>
       <c r="G82" s="26"/>
@@ -8356,7 +8356,7 @@
       <c r="Q82" s="28"/>
       <c r="R82" s="26"/>
     </row>
-    <row r="83" spans="1:18">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" s="25"/>
       <c r="B83" s="25"/>
       <c r="G83" s="26"/>
@@ -8369,7 +8369,7 @@
       <c r="Q83" s="28"/>
       <c r="R83" s="26"/>
     </row>
-    <row r="84" spans="1:18">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="25"/>
       <c r="B84" s="25"/>
       <c r="G84" s="26"/>
@@ -8382,7 +8382,7 @@
       <c r="Q84" s="28"/>
       <c r="R84" s="26"/>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="25"/>
       <c r="B85" s="25"/>
       <c r="G85" s="26"/>
@@ -8395,7 +8395,7 @@
       <c r="Q85" s="28"/>
       <c r="R85" s="26"/>
     </row>
-    <row r="86" spans="1:18">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="25"/>
       <c r="B86" s="25"/>
       <c r="G86" s="26"/>
@@ -8408,7 +8408,7 @@
       <c r="Q86" s="28"/>
       <c r="R86" s="26"/>
     </row>
-    <row r="87" spans="1:18">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="25"/>
       <c r="B87" s="25"/>
       <c r="G87" s="26"/>
@@ -8421,7 +8421,7 @@
       <c r="Q87" s="28"/>
       <c r="R87" s="26"/>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" s="25"/>
       <c r="B88" s="25"/>
       <c r="G88" s="26"/>
@@ -8434,7 +8434,7 @@
       <c r="Q88" s="28"/>
       <c r="R88" s="26"/>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="25"/>
       <c r="B89" s="25"/>
       <c r="G89" s="26"/>
@@ -8447,7 +8447,7 @@
       <c r="Q89" s="28"/>
       <c r="R89" s="26"/>
     </row>
-    <row r="90" spans="1:18">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="25"/>
       <c r="B90" s="25"/>
       <c r="G90" s="26"/>
@@ -8460,7 +8460,7 @@
       <c r="Q90" s="28"/>
       <c r="R90" s="26"/>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A91" s="25"/>
       <c r="B91" s="25"/>
       <c r="G91" s="26"/>
@@ -8473,7 +8473,7 @@
       <c r="Q91" s="28"/>
       <c r="R91" s="26"/>
     </row>
-    <row r="92" spans="1:18">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="25"/>
       <c r="B92" s="25"/>
       <c r="G92" s="26"/>
@@ -8486,7 +8486,7 @@
       <c r="Q92" s="28"/>
       <c r="R92" s="26"/>
     </row>
-    <row r="93" spans="1:18">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" s="25"/>
       <c r="B93" s="25"/>
       <c r="G93" s="26"/>
@@ -8499,7 +8499,7 @@
       <c r="Q93" s="28"/>
       <c r="R93" s="26"/>
     </row>
-    <row r="94" spans="1:18">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="25"/>
       <c r="B94" s="25"/>
       <c r="G94" s="26"/>
@@ -8512,7 +8512,7 @@
       <c r="Q94" s="28"/>
       <c r="R94" s="26"/>
     </row>
-    <row r="95" spans="1:18">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" s="25"/>
       <c r="B95" s="25"/>
       <c r="G95" s="26"/>
@@ -8525,7 +8525,7 @@
       <c r="Q95" s="28"/>
       <c r="R95" s="26"/>
     </row>
-    <row r="96" spans="1:18">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="25"/>
       <c r="B96" s="25"/>
       <c r="G96" s="26"/>
@@ -8538,7 +8538,7 @@
       <c r="Q96" s="28"/>
       <c r="R96" s="26"/>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A97" s="25"/>
       <c r="B97" s="25"/>
       <c r="G97" s="26"/>
@@ -8551,7 +8551,7 @@
       <c r="Q97" s="28"/>
       <c r="R97" s="26"/>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A98" s="25"/>
       <c r="B98" s="25"/>
       <c r="G98" s="26"/>
@@ -8564,7 +8564,7 @@
       <c r="Q98" s="28"/>
       <c r="R98" s="26"/>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" s="25"/>
       <c r="B99" s="25"/>
       <c r="G99" s="26"/>
@@ -8577,7 +8577,7 @@
       <c r="Q99" s="28"/>
       <c r="R99" s="26"/>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" s="25"/>
       <c r="B100" s="25"/>
       <c r="G100" s="26"/>
@@ -8590,7 +8590,7 @@
       <c r="Q100" s="28"/>
       <c r="R100" s="26"/>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" s="25"/>
       <c r="B101" s="25"/>
       <c r="G101" s="26"/>
@@ -8603,7 +8603,7 @@
       <c r="Q101" s="28"/>
       <c r="R101" s="26"/>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" s="25"/>
       <c r="B102" s="25"/>
       <c r="G102" s="26"/>
@@ -8616,7 +8616,7 @@
       <c r="Q102" s="28"/>
       <c r="R102" s="26"/>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A103" s="25"/>
       <c r="B103" s="25"/>
       <c r="G103" s="26"/>
@@ -8629,7 +8629,7 @@
       <c r="Q103" s="28"/>
       <c r="R103" s="26"/>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" s="25"/>
       <c r="B104" s="25"/>
       <c r="G104" s="26"/>
@@ -8642,7 +8642,7 @@
       <c r="Q104" s="28"/>
       <c r="R104" s="26"/>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A105" s="25"/>
       <c r="B105" s="25"/>
       <c r="G105" s="26"/>
@@ -8655,7 +8655,7 @@
       <c r="Q105" s="28"/>
       <c r="R105" s="26"/>
     </row>
-    <row r="106" spans="1:18">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" s="25"/>
       <c r="B106" s="25"/>
       <c r="G106" s="26"/>
@@ -8668,7 +8668,7 @@
       <c r="Q106" s="28"/>
       <c r="R106" s="26"/>
     </row>
-    <row r="107" spans="1:18">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A107" s="25"/>
       <c r="B107" s="25"/>
       <c r="G107" s="26"/>
@@ -8681,7 +8681,7 @@
       <c r="Q107" s="28"/>
       <c r="R107" s="26"/>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" s="25"/>
       <c r="B108" s="25"/>
       <c r="G108" s="26"/>
@@ -8694,7 +8694,7 @@
       <c r="Q108" s="28"/>
       <c r="R108" s="26"/>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A109" s="25"/>
       <c r="B109" s="25"/>
       <c r="G109" s="26"/>
@@ -8707,7 +8707,7 @@
       <c r="Q109" s="28"/>
       <c r="R109" s="26"/>
     </row>
-    <row r="110" spans="1:18">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" s="25"/>
       <c r="B110" s="25"/>
       <c r="G110" s="26"/>
@@ -8720,7 +8720,7 @@
       <c r="Q110" s="28"/>
       <c r="R110" s="26"/>
     </row>
-    <row r="111" spans="1:18">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A111" s="25"/>
       <c r="B111" s="25"/>
       <c r="G111" s="26"/>
@@ -8733,7 +8733,7 @@
       <c r="Q111" s="28"/>
       <c r="R111" s="26"/>
     </row>
-    <row r="112" spans="1:18">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" s="25"/>
       <c r="B112" s="25"/>
       <c r="G112" s="26"/>
@@ -8806,17 +8806,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.453125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" style="27" customWidth="1"/>
+    <col min="1" max="2" width="9.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="27" customWidth="1"/>
     <col min="5" max="5" width="24" style="27" customWidth="1"/>
-    <col min="6" max="6" width="33.453125" style="27" customWidth="1"/>
-    <col min="7" max="16384" width="9.1796875" style="27"/>
+    <col min="6" max="6" width="33.5" style="27" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="91.75" customHeight="1">
+    <row r="1" spans="1:6" ht="91.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="47" t="s">
         <v>213</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
         <v>89</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
         <v>89</v>
       </c>
@@ -8876,7 +8876,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="44" t="s">
         <v>89</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="44" t="s">
         <v>89</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="44" t="s">
         <v>89</v>
       </c>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="F6" s="30"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
         <v>89</v>
       </c>
@@ -8970,23 +8970,23 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.1796875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="17.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.1640625" style="6" customWidth="1"/>
     <col min="3" max="3" width="6" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.1796875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.1796875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.453125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="8.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.1640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5" style="6" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" style="6"/>
-    <col min="11" max="11" width="13.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>34</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>35</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -9060,7 +9060,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -9071,18 +9071,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E6" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E7" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E8" s="6" t="s">
         <v>40</v>
       </c>
@@ -9101,21 +9101,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007C69FE739999C447A76F1EF8B3FD66E4" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cbd048430c8551c34c2c3c8571f1b260">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4655c133-e14e-4d88-8fbc-c3b347145ec5" xmlns:ns4="64ced670-a384-4657-ba0f-fc07d30f5a44" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5457dbb80d17598a17de4d439e456cf2" ns3:_="" ns4:_="">
     <xsd:import namespace="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
@@ -9338,32 +9323,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6264E33-6917-4678-8EC8-8D88A2F9795C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A51E5E2-41F2-4A1F-A4B0-950DEDB4B143}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
-    <ds:schemaRef ds:uri="64ced670-a384-4657-ba0f-fc07d30f5a44"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1C9E008-75C3-4280-8CCC-7498B59407BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9380,4 +9355,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6264E33-6917-4678-8EC8-8D88A2F9795C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A51E5E2-41F2-4A1F-A4B0-950DEDB4B143}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
+    <ds:schemaRef ds:uri="64ced670-a384-4657-ba0f-fc07d30f5a44"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>